--- a/benchmark/generated_files/CRED-1_V_035.xlsx
+++ b/benchmark/generated_files/CRED-1_V_035.xlsx
@@ -453,194 +453,194 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>46024</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>46026</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 324,67 EUR DEL 02.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 20,95 EUR DEL 01.01.2026 A (ITA) TIGOTÀ SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>324.67</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELEPASS PEDAGGI A14 AUTOSTRADA</t>
+          <t>Pagam. POS - PAGAMENTO POS 159,75 EUR DEL 02.01.2026 A (ITA) PANIFICIO TOSI</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>150.01</v>
+        <v>159.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>Pagam. POS - PAGAMENTO POS 175,86 EUR DEL 03.01.2026 A (ITA) BUREAU VALLÉE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>303.81</v>
+        <v>175.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46032</v>
+        <v>46027</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46034</v>
+        <v>46027</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 189,42 EUR DEL 10.01.2026 A (ITA) UDEMY.COM FORMAZIONE</t>
+          <t>Pagam. POS - PAGAMENTO POS 287,66 EUR DEL 05.01.2026 A (ITA) UNIEURO BOLOGNA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>189.42</v>
+        <v>287.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 113,12 EUR DEL 10.01.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>Disposizione - RIF:212780683 BEN. STUDIO COMM.LE FERRI &amp; ASSOCIATI</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>113.12</v>
+        <v>244.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46033</v>
+        <v>46030</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46033</v>
+        <v>46030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 364,39 EUR DEL 11.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5102 AS 24 EUR</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>364.39</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>46037</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Addebito SDD - JETBRAINS S.R.O. INTELLIJ IDEA</t>
+          <t>Pagam. POS - PAGAMENTO POS 145,66 EUR DEL 15.01.2026 A (ITA) COOP</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>128.86</v>
+        <v>145.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Addebito SDD - SPOTIFY AB</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>43.72</v>
+        <v>246.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 390,59 EUR DEL 14.01.2026 A (ITA) BAGNO MARINO N.42 RICCIONE</t>
+          <t>Pagam. POS - PAGAMENTO POS 127,57 EUR DEL 16.01.2026 A (ITA) ACQUA &amp; SAPONE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>390.59</v>
+        <v>127.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46037</v>
+        <v>46039</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>46039</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 491,45 EUR DEL 15.01.2026 A (ITA) RYANAIR LTD</t>
+          <t>Pagam. POS - PAGAMENTO POS 117,21 EUR DEL 17.01.2026 A (ITA) TIGOTÀ FLAMINIO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>491.45</v>
+        <v>117.21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46041</v>
+        <v>46039</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46041</v>
+        <v>46039</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 223,83 EUR DEL 19.01.2026 A (ITA) HOTEL BELLAVISTA RIMINI</t>
+          <t>Pagam. POS - PAGAMENTO POS 10,02 EUR DEL 17.01.2026 A (ITA) PIZZERIA NAPOLI</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>223.83</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46043</v>
+        <v>46040</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46043</v>
+        <v>46040</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 97,93 EUR DEL 21.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2367 L'ISOLA DEI TESORI</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>97.93000000000001</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="14">
@@ -648,351 +648,351 @@
         <v>46043</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 117,79 EUR DEL 21.01.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 317,29 EUR DEL 21.01.2026 A (ITA) BAGNO MARINO N.42 RICCIONE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>117.79</v>
+        <v>317.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Addebito SDD - ACI BOLLO AUTO TARGA MD751EL</t>
+          <t>Pagam. POS - PAGAMENTO POS 125,29 EUR DEL 22.01.2026 A (ITA) BUREAU VALLÉE CAGLIARI</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>83.27</v>
+        <v>125.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46047</v>
+        <v>46045</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46047</v>
+        <v>46045</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 7297 LIDL ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 94,67 EUR DEL 23.01.2026 A (ITA) GABOR</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>121.48</v>
+        <v>94.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46048</v>
+        <v>46046</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46049</v>
+        <v>46046</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8900 NHOW</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>67.13</v>
+        <v>200.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 96,53 EUR DEL 26.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 16,49 EUR DEL 30.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>96.53</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46049</v>
+        <v>46054</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46049</v>
+        <v>46054</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4810 CADDY'S PADOVA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>325.24</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 98,81 EUR DEL 27.01.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>AMAZON.IT MARKETPLACE HW - ORDINE 402-216455399</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>98.81</v>
+        <v>247.81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46051</v>
+        <v>46060</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 121,94 EUR DEL 27.01.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 380,03 EUR DEL 06.02.2026 A (ITA) CEX</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>121.94</v>
+        <v>380.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46050</v>
+        <v>46059</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46051</v>
+        <v>46059</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELEPASS PEDAGGI A14 AUTOSTRADA</t>
+          <t>Pagam. POS - PAGAMENTO POS 24,41 EUR DEL 06.02.2026 A (ITA) NATURA ASSAGO</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>498.23</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46051</v>
+        <v>46060</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46053</v>
+        <v>46060</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 96,35 EUR DEL 29.01.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 139,38 EUR DEL 07.02.2026 A (ITA) BUFFETTI</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>96.34999999999999</v>
+        <v>139.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46052</v>
+        <v>46062</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 75,59 EUR DEL 30.01.2026 A (ITA) BAR CENTRALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 96,85 EUR DEL 09.02.2026 A (ITA) SPLENDIDI E SPLENDENTI</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75.59</v>
+        <v>96.84999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46053</v>
+        <v>46062</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46054</v>
+        <v>46062</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 41,19 EUR DEL 31.01.2026 A (ITA) BAR CENTRALE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7240 TACO BELL VERONA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.19</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46054</v>
+        <v>46063</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46054</v>
+        <v>46063</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 57,36 EUR DEL 01.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>Pagam. POS - PAGAMENTO POS 48,99 EUR DEL 10.02.2026 A (ITA) RISTORANTE DA GINO</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>57.36</v>
+        <v>48.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46056</v>
+        <v>46066</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46057</v>
+        <v>46066</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 264,42 EUR DEL 03.02.2026 A (ITA) BAGNO MARINO N.42 RICCIONE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6482 ARCAPLANET BERGAMO</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>264.42</v>
+        <v>90.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46059</v>
+        <v>46067</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46059</v>
+        <v>46067</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2633 ALL'ANTICO VINAIO EUR</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>380.18</v>
+        <v>24.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46060</v>
+        <v>46067</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46061</v>
+        <v>46068</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 29,23 EUR DEL 07.02.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 21,25 EUR DEL 14.02.2026 A (ITA) ZARA ITALIA SRL</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.23</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46064</v>
+        <v>46067</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46064</v>
+        <v>46069</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 132,10 EUR DEL 11.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>Pagam. POS - PAGAMENTO POS 192,88 EUR DEL 14.02.2026 A (ITA) LEONARDO HOTELS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>132.1</v>
+        <v>192.88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46064</v>
+        <v>46068</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46064</v>
+        <v>46068</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 189,47 EUR DEL 11.02.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>AMAZON.IT MARKETPLACE HW - ORDINE 402-215686835</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>189.47</v>
+        <v>258.96</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46064</v>
+        <v>46069</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 55,10 EUR DEL 11.02.2026 A (ITA) BAGNO MARINO N.42 RICCIONE</t>
+          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>55.1</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46067</v>
+        <v>46070</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>Addebito SDD - SPOTIFY AB</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>339.14</v>
+        <v>127.05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46067</v>
+        <v>46071</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46067</v>
+        <v>46073</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-211638758</t>
+          <t>Pagam. POS - PAGAMENTO POS 59,66 EUR DEL 18.02.2026 A (ITA) GNP CORSICO</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>204.39</v>
+        <v>59.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46068</v>
+        <v>46071</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46069</v>
+        <v>46073</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:212181070 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>Pagam. POS - PAGAMENTO POS 59,52 EUR DEL 18.02.2026 A (ITA) STAZIONE Q8</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>67.39</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="36">
@@ -1000,15 +1000,15 @@
         <v>46072</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8278 GULLIVER</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>75.02</v>
+        <v>159.7</v>
       </c>
     </row>
     <row r="37">
@@ -1020,75 +1020,75 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 9,64 EUR DEL 20.02.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6411 OCCIDENTAL BOLOGNA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9.640000000000001</v>
+        <v>75.65000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 2619 OVS S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8490 BUREAU VALLÉE FIRENZE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>88.36</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46076</v>
+        <v>46074</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46076</v>
+        <v>46074</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 271,27 EUR DEL 23.02.2026 A (ITA) UDEMY.COM FORMAZIONE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8295 NATURA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>271.27</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Addebito SDD - JETBRAINS S.R.O. INTELLIJ IDEA</t>
+          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>37.8</v>
+        <v>59.07</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46081</v>
+        <v>46079</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46081</v>
+        <v>46079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-211504028</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3589 INMOTION MESTRE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>65.06</v>
+        <v>378.75</v>
       </c>
     </row>
   </sheetData>
